--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -520,8 +520,9 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,10 +553,15 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Feeds From</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -585,6 +591,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -614,10 +621,15 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>LBS</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>MV1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Feeds RMU2 and RMU3</t>
         </is>
@@ -651,10 +663,15 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>LBS</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>RMU1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -684,10 +701,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>LBS, LBS</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>RMU1, RMU2</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Ring closed via RMU2</t>
         </is>
@@ -721,10 +743,15 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>Fuse-switch</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>RMU2</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -754,10 +781,15 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>Fuse-switch</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>RMU3</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -787,10 +819,15 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>TX1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -820,10 +857,15 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>TX1</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -853,10 +895,15 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>TX2</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -886,10 +933,15 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>TX2</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -919,10 +971,15 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>LVP1</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -952,10 +1009,15 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>LVP1</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -985,10 +1047,15 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>LVP2</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1018,10 +1085,15 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>LVP2</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1051,10 +1123,15 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>LVP3</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1084,10 +1161,15 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>LVP3</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1117,10 +1199,15 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>LVP4</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1150,10 +1237,15 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>LVP4</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1163,6 +1255,7 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1172,6 +1265,7 @@
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1181,6 +1275,7 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1190,6 +1285,7 @@
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1199,6 +1295,7 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1208,6 +1305,7 @@
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1217,6 +1315,7 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1226,6 +1325,7 @@
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1235,6 +1335,7 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1244,6 +1345,7 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1253,11 +1355,15 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
       <formula1>"MV Incomer,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1270,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1366,33 +1472,68 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch or Contactor, or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1363,7 +1363,7 @@
       <formula1>"MV Incomer,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor"</formula1>
+      <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor,Fuse-contactor"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1479,61 +1479,68 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch or Contactor, or leave blank for</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1359,8 +1359,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
-      <formula1>"MV Incomer,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
+      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor,Fuse-contactor"</formula1>
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1423,124 +1423,131 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Type: pick from the dropdown (MV Incomer, MV Busbar, RMU,</t>
+          <t xml:space="preserve">   - Type: pick from the dropdown (MV Incomer, Generator, MV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler).</t>
+          <t xml:space="preserve">     Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
+          <t xml:space="preserve">     Bus Coupler).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
+          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
+          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1359,8 +1359,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
-      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, SU Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
+      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,SU Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor,Fuse-contactor"</formula1>
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1430,124 +1430,152 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC,</t>
+          <t xml:space="preserve">     Busbar, RMU, Transformer, SU Transformer, Pump, LV Busbar,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Bus Coupler).</t>
+          <t xml:space="preserve">     Feeder, MCC, Bus Coupler).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
+          <t xml:space="preserve">     SU Transformer = a step-up drawn hanging UNDER its MV board</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
+          <t xml:space="preserve">     (Feeds From = that board), with its generator below it</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
+          <t xml:space="preserve">     (the generator's Feeds From = the SU Transformer). A plain</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">     Transformer that feeds an MV board is drawn above it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1359,8 +1359,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, SU Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
-      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,SU Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
+      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor,Fuse-contactor"</formula1>
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1430,152 +1430,166 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Busbar, RMU, Transformer, SU Transformer, Pump, LV Busbar,</t>
+          <t xml:space="preserve">     Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Feeder, MCC, Bus Coupler).</t>
+          <t xml:space="preserve">     Bus Coupler).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     SU Transformer = a step-up drawn hanging UNDER its MV board</t>
+          <t xml:space="preserve">     One Transformer type covers step-down and step-up: which</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (Feeds From = that board), with its generator below it</t>
+          <t xml:space="preserve">     way it is drawn follows Feeds From. A transformer that</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (the generator's Feeds From = the SU Transformer). A plain</t>
+          <t xml:space="preserve">     feeds an MV board is a step-up, drawn above it with its</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Transformer that feeds an MV board is drawn above it.</t>
+          <t xml:space="preserve">     source on top; one hung under an MV board whose load is a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
+          <t xml:space="preserve">     Generator is the same step-up drawn upside down. Write</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
+          <t xml:space="preserve">     'step-up' in Description - the voltages say it too.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
+          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1359,8 +1359,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler" type="list">
-      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler"</formula1>
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown type" error="Pick one of: MV Incomer, Generator, MV Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC, Bus Coupler, Capacitor Bank, Earthing/NER, Surge Arrester" type="list">
+      <formula1>"MV Incomer,Generator,MV Busbar,RMU,Transformer,Pump,LV Busbar,Feeder,MCC,Bus Coupler,Capacitor Bank,Earthing/NER,Surge Arrester"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CB,LBS,Fuse,Fuse-switch,Contactor,Fuse-contactor"</formula1>
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1437,7 +1437,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Bus Coupler).</t>
+          <t xml:space="preserve">     Bus Coupler, Capacitor Bank, Earthing/NER, Surge Arrester).</t>
         </is>
       </c>
     </row>
@@ -1500,96 +1500,159 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie.</t>
+          <t xml:space="preserve">     between two MV Busbars is the bus tie; one between a board</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">     and a Generator is a changeover (ATS). A Generator can also</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">     feed a board directly: name it in the board's Feeds From.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">     An LV Busbar fed from a Feeder or another LV Busbar is a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">     sub-board, drawn on the row below. A Feeder on MV gear is</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">     an outgoing cable way. Capacitor Bank, Earthing/NER and</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     Surge Arrester need no load; a Feeder whose words say</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">     capacitor / NER / arrester is drawn as one anyway.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     Notes: 'VSD' on a motor draws a drive box, 'Spare' dashes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     the way, 'N.O.' on an RMU marks the ring's open point.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1493,166 +1493,173 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MCC = motor control centre on an LV board. A Bus Coupler</t>
+          <t xml:space="preserve">     MCC = motor control centre on an LV board; a Pump or Feeder</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie; one between a board</t>
+          <t xml:space="preserve">     can feed from an MCC and hangs off its own bus. A Bus Coupler</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     and a Generator is a changeover (ATS). A Generator can also</t>
+          <t xml:space="preserve">     between two MV Busbars is the bus tie; one between a board</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     feed a board directly: name it in the board's Feeds From.</t>
+          <t xml:space="preserve">     and a Generator is a changeover (ATS). A Generator can also</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     An LV Busbar fed from a Feeder or another LV Busbar is a</t>
+          <t xml:space="preserve">     feed a board directly: name it in the board's Feeds From.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     sub-board, drawn on the row below. A Feeder on MV gear is</t>
+          <t xml:space="preserve">     An LV Busbar fed from a Feeder or another LV Busbar is a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     an outgoing cable way. Capacitor Bank, Earthing/NER and</t>
+          <t xml:space="preserve">     sub-board, drawn on the row below. A Feeder on MV gear is</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Surge Arrester need no load; a Feeder whose words say</t>
+          <t xml:space="preserve">     an outgoing cable way. Capacitor Bank, Earthing/NER and</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     capacitor / NER / arrester is drawn as one anyway.</t>
+          <t xml:space="preserve">     Surge Arrester need no load; a Feeder whose words say</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Notes: 'VSD' on a motor draws a drive box, 'Spare' dashes</t>
+          <t xml:space="preserve">     capacitor / NER / arrester is drawn as one anyway.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the way, 'N.O.' on an RMU marks the ring's open point.</t>
+          <t xml:space="preserve">     Notes: 'VSD' on a motor draws a drive box, 'Spare' dashes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">     the way, 'N.O.' on an RMU marks the ring's open point.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
         </is>

--- a/examples/config6_closed_ring.xlsx
+++ b/examples/config6_closed_ring.xlsx
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1402,266 +1402,617 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1. Info sheet: site name, date, surveyor, free notes.</t>
+          <t>One row per item, top of the network first. The drawing's topology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2. Equipment sheet: one row per item, top of the network first.</t>
+          <t>comes only from ID and Feeds From: an item is drawn under whatever it</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - ID: short unique tag you invent (MV1, RMU1, TX1, BB1, F1...).</t>
+          <t>feeds from. Row order sets left-to-right order. A half-filled row still</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Type: pick from the dropdown (MV Incomer, Generator, MV</t>
+          <t>draws, with an open terminal where the supply or the load is missing.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Busbar, RMU, Transformer, Pump, LV Busbar, Feeder, MCC,</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Bus Coupler, Capacitor Bank, Earthing/NER, Surge Arrester).</t>
+          <t>COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     One Transformer type covers step-down and step-up: which</t>
+          <t xml:space="preserve">  ID          a short unique tag you invent: MV1, RMU1, TX1, BB1, F1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     way it is drawn follows Feeds From. A transformer that</t>
+          <t xml:space="preserve">  Type        pick from the dropdown (see TYPES)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     feeds an MV board is a step-up, drawn above it with its</t>
+          <t xml:space="preserve">  Description free text, printed as a label (a few words also change</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     source on top; one hung under an MV board whose load is a</t>
+          <t xml:space="preserve">              the symbol - see WORDS)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Generator is the same step-up drawn upside down. Write</t>
+          <t xml:space="preserve">  Rating      from the nameplate: 1000 kVA, 630 A, 315 kW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     'step-up' in Description - the voltages say it too.</t>
+          <t xml:space="preserve">  Voltage     from the nameplate: 11/0.4 kV, 400 V - printed only</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV Busbar = an MV switchboard; Pump = an MV motor load;</t>
+          <t xml:space="preserve">  Protection  the device on THIS item's supply side: CB, LBS, Fuse,</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MCC = motor control centre on an LV board; a Pump or Feeder</t>
+          <t xml:space="preserve">              Fuse-switch, Contactor, Fuse-contactor; blank = the usual</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     can feed from an MCC and hangs off its own bus. A Bus Coupler</t>
+          <t xml:space="preserve">              default; two supplies: a comma list in Feeds From order</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     between two MV Busbars is the bus tie; one between a board</t>
+          <t xml:space="preserve">              (LBS, CB). Free text on a busbar (87B differential) is</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     and a Generator is a changeover (ATS). A Generator can also</t>
+          <t xml:space="preserve">              printed as a zone label.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     feed a board directly: name it in the board's Feeds From.</t>
+          <t xml:space="preserve">  Feeds From  the ID of the item supplying this one; comma for two</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     An LV Busbar fed from a Feeder or another LV Busbar is a</t>
+          <t xml:space="preserve">              supplies (BB1, BB2 - MV1, MV2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     sub-board, drawn on the row below. A Feeder on MV gear is</t>
+          <t xml:space="preserve">  Notes       anything worth remembering; printed on ties; a few</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     an outgoing cable way. Capacitor Bank, Earthing/NER and</t>
+          <t xml:space="preserve">              leading words change the symbol - see WORDS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Surge Arrester need no load; a Feeder whose words say</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     capacitor / NER / arrester is drawn as one anyway.</t>
+          <t>TYPES (and how each one draws)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Notes: 'VSD' on a motor draws a drive box, 'Spare' dashes</t>
+          <t xml:space="preserve">  MV Incomer     source tick at the top; feeds an MV Busbar, RMU or TX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the way, 'N.O.' on an RMU marks the ring's open point.</t>
+          <t xml:space="preserve">  MV Busbar      thick bar, a breaker on every way; a board fed from</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Rating / Voltage: as read from the nameplate (e.g. 1000 kVA,</t>
+          <t xml:space="preserve">                 another board sits one tier lower</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     11/0.4 kV, 630 A, 400 V).</t>
+          <t xml:space="preserve">  RMU            dashed enclosure, load-break switches on the ways in,</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Protection: the device on THIS item's supply side - pick</t>
+          <t xml:space="preserve">                 fuse-switches on the tee-offs; RMUs that feed from</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     CB, LBS, Fuse, Fuse-switch, Contactor or Fuse-contactor (an</t>
+          <t xml:space="preserve">                 each other form a ring side by side</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     MV motor starter = fuse + contactor), or leave blank for</t>
+          <t xml:space="preserve">  Transformer    two circles; step-down or step-up follows Feeds From</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the usual default. Two supplies: comma list in the same</t>
+          <t xml:space="preserve">  Generator      G circle over the board it feeds, on top of a step-up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     order as Feeds From (e.g. LBS, CB). Free text on a busbar</t>
+          <t xml:space="preserve">                 column, or under a reversed one</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (e.g. 87B differential) is printed next to its label.</t>
+          <t xml:space="preserve">  Pump           M 3~ circle: transformer row on MV gear, feeder band</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Feeds From: the ID of the item supplying this one. Use a comma</t>
+          <t xml:space="preserve">                 on an LV board or an MCC, under a transformer of its own</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     for two supplies (bus coupler between BB1, BB2 - or an RMU fed</t>
+          <t xml:space="preserve">  LV Busbar      thick bar with its feeders; fed from a Feeder or</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     by ring incomers MV1, MV2).</t>
+          <t xml:space="preserve">                 another LV Busbar it is a sub-board on the row below</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3. Back at the office:  python sld_sketch.py thisfile.xlsx</t>
+          <t xml:space="preserve">  Feeder         drop + device + arrow; on MV gear an outgoing cable</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and you get the single-line diagram as an SVG.</t>
+          <t xml:space="preserve">  MCC            labelled box; with Pumps/Feeders under it, a bus of</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 its own on the row below with the motor ways off it</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bus Coupler    breaker between two busbars of the same kind; between</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 a board and a Generator, a changeover (ATS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capacitor Bank plates to earth (LV board or MV gear); needs no load</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Earthing/NER   resistor box to earth; needs no load</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Surge Arrester arrester box to earth; needs no load</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>WIRING RECIPES (Feeds From)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step-down: TX feeds from the MV board/RMU; the LV Busbar from TX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step-up from a genset or PV board: TX feeds from the Generator (or</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    generation LV Busbar); the MV Busbar/RMU feeds from TX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step-up from a live LV board: TX feeds from that board; the MV</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    gear feeds from TX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Genset straight onto a board: the board feeds from MV, DG1, DG2;</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the Generator rows have Feeds From blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Standby set on a changeover: a Bus Coupler row ATS feeding from</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MSB3, G1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sub-board (DB): the LV Busbar feeds from the Feeder that supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    it, or straight from the main LV Busbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Motors in an MCC: the MCC feeds from the board; each Pump from the MCC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bus tie: a Bus Coupler feeding from BB1, BB2; Notes Normally open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Board with two supplies: the board feeds from TX1, TX2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ring of RMUs from a board: each RMU feeds from its neighbours</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (PB, R2 ... R4, PB); a link written on both rows is drawn once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Open point of a ring: Notes on one RMU: N.O. towards RMU2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spur or sub-ring off an RMU: the spur RMU feeds from the ring RMU;</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    a sub-ring's two RMUs feed from it and from each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Several voltage levels: the lower board feeds from the transformer,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the transformer from the upper board; tiers follow the wiring,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    never the Voltage column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Outgoing MV cable, capacitor bank, NER: a Feeder, Capacitor Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    or Earthing/NER row feeding from the MV board or RMU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>WORDS THAT CHANGE THE SYMBOL (read from Description and Notes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VSD / VFD / drive        on a Pump: a drive box on the motor's drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spare / Future /         at the start of Notes: the way drawn dashed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Out of service</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  N.O. / Normally open     on a Bus Coupler: printed under it</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  N.O. towards RMU2,       on an RMU: an N.O. marker on the cable to</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ring open here           the RMU named, or under the box</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  capacitor / PFC / kvar   on a Feeder: drawn as a capacitor bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NER / earthing / zig-zag on a Feeder, or a Transformer with nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                           on its output: earthing resistor / tx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  arrester / surge         on a Feeder: drawn as a surge arrester</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Protection words: CB MCCB MCB ACB - LBS isolator - Fuse -</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fuse-switch SFU - Contactor - Fuse-contactor starter</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>BACK AT THE OFFICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python sld_sketch.py thisfile.xlsx           -&gt; the SVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python sld_sketch.py thisfile.xlsx --dxf     -&gt; SVG + DXF with the</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                  equipment table</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python sld_check.py thisfile.xlsx            -&gt; checks the drawing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                  against the table</t>
         </is>
       </c>
     </row>
